--- a/target.xlsx
+++ b/target.xlsx
@@ -8,44 +8,168 @@
   </bookViews>
   <sheets>
     <sheet name="1_OS설치" sheetId="1" r:id="rId1"/>
-    <sheet name="2_네트워크구성" sheetId="2" r:id="rId4"/>
-    <sheet name="3_보안점검" sheetId="3" r:id="rId5"/>
+    <sheet name="2_네트워크설정" sheetId="2" r:id="rId5"/>
+    <sheet name="3_보안점검" sheetId="3" r:id="rId6"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
-  <si>
-    <t>1. ISO 이미지 마운트 및 UEFI 부팅
-2. 파티션 구성:
-   - /boot: 1024MB (xfs)
-   - swap: 4096MB
-   - /: 나머지 전체 용량 할당
-3. 관리자(root) 패스워드 설정 및 설치 시작</t>
-  </si>
-  <si>
-    <t>1. 물리 NIC 확인 (ens192, ens224)
-2. LACP(Mode 4) 본딩 bond0 생성
-   - IP: 192.168.10.50/24
-   - Gateway: 192.168.10.1
-   - DNS: 168.126.63.1, 8.8.8.8
-3. 게이트웨이 핑 테스트 및 외부 통신 확인</t>
-  </si>
-  <si>
-    <t>1. SSH 원격 접속 보안 설정:
-   - /etc/ssh/sshd_config -&gt; PermitRootLogin no
-2. firewalld 방화벽 활성화 및 포트 제어:
-   - 허용 포트: 22(SSH), 443(HTTPS)
-3. SELinux enforcing 상태 확인 완료</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+  <si>
+    <t>사전작업</t>
+  </si>
+  <si>
+    <t>Step</t>
+  </si>
+  <si>
+    <t>작업내용</t>
+  </si>
+  <si>
+    <t>작업자에 의한 사전 작업 내용</t>
+  </si>
+  <si>
+    <t>작업대상</t>
+  </si>
+  <si>
+    <t>검증방법</t>
+  </si>
+  <si>
+    <t>작업자</t>
+  </si>
+  <si>
+    <t>검증자</t>
+  </si>
+  <si>
+    <t>작업결과</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>OS 설치 사전 준비
+- ISO 이미지 무결성 확인</t>
+  </si>
+  <si>
+    <t>설치 대상 서버 전원/콘솔 확인
+- iDRAC 접속 계정 확인</t>
+  </si>
+  <si>
+    <t>샘플대상</t>
+  </si>
+  <si>
+    <t>sha256sum 결과 비교</t>
+  </si>
+  <si>
+    <t>샘플작업자</t>
+  </si>
+  <si>
+    <t>샘플검증자</t>
+  </si>
+  <si>
+    <t>본작업</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>OS 설치 진행
+- UEFI 부팅 후 파티션 구성
+- /boot 1GB, swap 4GB</t>
+  </si>
+  <si>
+    <t>설치 화면 캡처 첨부</t>
+  </si>
+  <si>
+    <t>설치 완료 후 재부팅 확인</t>
+  </si>
+  <si>
+    <t>사후작업</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>OS 기본 설정
+- 호스트명/시간대 설정</t>
+  </si>
+  <si>
+    <t>설정 파일 백업
+- /etc/hosts 백업</t>
+  </si>
+  <si>
+    <t>hostnamectl 결과 확인</t>
+  </si>
+  <si>
+    <t>네트워크 사전 점검
+- 물리 NIC 링크 상태 확인</t>
+  </si>
+  <si>
+    <t>스위치 포트 VLAN 확인 요청</t>
+  </si>
+  <si>
+    <t>ethtool 링크 Up 확인</t>
+  </si>
+  <si>
+    <t>본딩 구성
+- bond0 (LACP mode 4)
+- IP 192.168.10.50/24</t>
+  </si>
+  <si>
+    <t>구성도 첨부</t>
+  </si>
+  <si>
+    <t>게이트웨이 ping 응답 확인</t>
+  </si>
+  <si>
+    <t>네트워크 설정 저장
+- nmcli 연결 프로필 저장</t>
+  </si>
+  <si>
+    <t>기존 설정 백업 파일 보관</t>
+  </si>
+  <si>
+    <t>재부팅 후 IP 유지 확인</t>
+  </si>
+  <si>
+    <t>보안 점검 사전 준비
+- 점검 스크립트 배포</t>
+  </si>
+  <si>
+    <t>점검 일정 공지
+- 담당자 승인 확인</t>
+  </si>
+  <si>
+    <t>스크립트 실행 권한 확인</t>
+  </si>
+  <si>
+    <t>보안 설정 적용
+- PermitRootLogin no
+- firewalld 22/443 허용</t>
+  </si>
+  <si>
+    <t>적용 전 설정 화면 첨부</t>
+  </si>
+  <si>
+    <t>sshd -T 결과 확인</t>
+  </si>
+  <si>
+    <t>보안 점검 결과 정리
+- SELinux enforcing 확인</t>
+  </si>
+  <si>
+    <t>점검 결과 보고서 작성</t>
+  </si>
+  <si>
+    <t>점검 결과 화면 확인</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -55,11 +179,24 @@
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
-      <color rgb="FF1E293B"/>
+      <b val="1"/>
+      <color/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <color/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <color/>
+      <sz val="14"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -68,7 +205,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8FAFC"/>
+        <fgColor rgb="FFDCE6F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,26 +224,38 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF94A3B8"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color rgb="FF94A3B8"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color rgb="FF94A3B8"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF94A3B8"/>
+        <color rgb="FF000000"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -116,16 +270,16 @@
 <xdr:wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1428750</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -143,7 +297,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="1828800" cy="457200"/>
+          <a:ext cx="1371600" cy="342900"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
       </xdr:spPr>
@@ -157,16 +311,16 @@
 <xdr:wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1428750</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -184,7 +338,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="1828800" cy="457200"/>
+          <a:ext cx="1371600" cy="342900"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
       </xdr:spPr>
@@ -198,16 +352,16 @@
 <xdr:wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1428750</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -225,7 +379,43 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="1828800" cy="457200"/>
+          <a:ext cx="1371600" cy="342900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="true" fPrintsWithSheet="true"/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1428750</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 3" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="false"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1371600" cy="342900"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
       </xdr:spPr>
@@ -496,57 +686,383 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="7" min="1" width="10"/>
-    <col customWidth="true" max="11" min="8" width="24"/>
+    <col customWidth="true" max="1" min="1" width="3"/>
+    <col customWidth="true" max="2" min="2" width="8"/>
+    <col customWidth="true" max="3" min="3" width="30"/>
+    <col customWidth="true" max="4" min="4" width="28.25"/>
+    <col customWidth="true" max="5" min="5" width="14"/>
+    <col customWidth="true" max="6" min="6" width="30"/>
+    <col customWidth="true" max="8" min="7" width="10"/>
+    <col customWidth="true" max="9" min="9" width="12"/>
   </cols>
   <sheetData>
     <row r="2" ht="22" customHeight="true">
-      <c r="H2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
       <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-    </row>
-    <row r="3" ht="22" customHeight="true">
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-    </row>
-    <row r="4" ht="22" customHeight="true">
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-    </row>
-    <row r="5" ht="22" customHeight="true">
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-    </row>
-    <row r="6" ht="22" customHeight="true">
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-    </row>
-    <row r="7" ht="22" customHeight="true">
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-    </row>
-    <row r="8" ht="22" customHeight="true">
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
+    </row>
+    <row r="3" ht="33" customHeight="true">
+      <c r="B3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="true">
+      <c r="B4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="5"/>
+    </row>
+    <row r="5" ht="24" customHeight="true">
+      <c r="B5" s="5"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+    </row>
+    <row r="6" ht="24" customHeight="true">
+      <c r="B6" s="5"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+    </row>
+    <row r="7" ht="24" customHeight="true">
+      <c r="B7" s="5"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+    </row>
+    <row r="11" ht="22" customHeight="true">
+      <c r="B11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+    </row>
+    <row r="13" ht="33" customHeight="true">
+      <c r="B13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="true">
+      <c r="B14" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" s="5"/>
+    </row>
+    <row r="15" ht="24" customHeight="true">
+      <c r="B15" s="5"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+    </row>
+    <row r="16" ht="24" customHeight="true">
+      <c r="B16" s="5"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+    </row>
+    <row r="17" ht="24" customHeight="true">
+      <c r="B17" s="5"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+    </row>
+    <row r="18" ht="24" customHeight="true">
+      <c r="B18" s="5"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+    </row>
+    <row r="19" ht="24" customHeight="true">
+      <c r="B19" s="5"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+    </row>
+    <row r="23" ht="22" customHeight="true">
+      <c r="B23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+    </row>
+    <row r="25" ht="33" customHeight="true">
+      <c r="B25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="true">
+      <c r="B26" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I26" s="5"/>
+    </row>
+    <row r="27" ht="24" customHeight="true">
+      <c r="B27" s="5"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+    </row>
+    <row r="28" ht="24" customHeight="true">
+      <c r="B28" s="5"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+    </row>
+    <row r="29" ht="24" customHeight="true">
+      <c r="B29" s="5"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+    </row>
+    <row r="30" ht="24" customHeight="true">
+      <c r="B30" s="5"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+    </row>
+    <row r="31" ht="24" customHeight="true">
+      <c r="B31" s="5"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="H2:K8"/>
+  <mergeCells count="29">
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="C4:C7"/>
+    <mergeCell ref="D4:D7"/>
+    <mergeCell ref="E4:E7"/>
+    <mergeCell ref="F4:F7"/>
+    <mergeCell ref="G4:G7"/>
+    <mergeCell ref="H4:H7"/>
+    <mergeCell ref="I4:I7"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="B14:B19"/>
+    <mergeCell ref="C14:C19"/>
+    <mergeCell ref="D14:D19"/>
+    <mergeCell ref="E14:E19"/>
+    <mergeCell ref="F14:F19"/>
+    <mergeCell ref="G14:G19"/>
+    <mergeCell ref="H14:H19"/>
+    <mergeCell ref="I14:I19"/>
+    <mergeCell ref="B23:I23"/>
+    <mergeCell ref="B24:I24"/>
+    <mergeCell ref="B26:B31"/>
+    <mergeCell ref="C26:C31"/>
+    <mergeCell ref="D26:D31"/>
+    <mergeCell ref="E26:E31"/>
+    <mergeCell ref="F26:F31"/>
+    <mergeCell ref="G26:G31"/>
+    <mergeCell ref="H26:H31"/>
+    <mergeCell ref="I26:I31"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -556,57 +1072,373 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="7" min="1" width="10"/>
-    <col customWidth="true" max="11" min="8" width="24"/>
+    <col customWidth="true" max="1" min="1" width="3"/>
+    <col customWidth="true" max="2" min="2" width="8"/>
+    <col customWidth="true" max="3" min="3" width="30"/>
+    <col customWidth="true" max="4" min="4" width="28.25"/>
+    <col customWidth="true" max="5" min="5" width="14"/>
+    <col customWidth="true" max="6" min="6" width="30"/>
+    <col customWidth="true" max="8" min="7" width="10"/>
+    <col customWidth="true" max="9" min="9" width="12"/>
   </cols>
   <sheetData>
-    <row r="2" ht="22" customHeight="true">
-      <c r="H2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-    </row>
-    <row r="3" ht="22" customHeight="true">
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-    </row>
     <row r="4" ht="22" customHeight="true">
+      <c r="B4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-    </row>
-    <row r="5" ht="22" customHeight="true">
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-    </row>
-    <row r="6" ht="22" customHeight="true">
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-    </row>
-    <row r="7" ht="22" customHeight="true">
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-    </row>
-    <row r="8" ht="22" customHeight="true">
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
+    </row>
+    <row r="5">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+    </row>
+    <row r="6" ht="33" customHeight="true">
+      <c r="B6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="true">
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="5"/>
+    </row>
+    <row r="8" ht="24" customHeight="true">
+      <c r="B8" s="5"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+    </row>
+    <row r="9" ht="24" customHeight="true">
+      <c r="B9" s="5"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+    </row>
+    <row r="10" ht="24" customHeight="true">
+      <c r="B10" s="5"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+    </row>
+    <row r="13" ht="22" customHeight="true">
+      <c r="B13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" ht="33" customHeight="true">
+      <c r="B14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="true">
+      <c r="B15" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I15" s="5"/>
+    </row>
+    <row r="16" ht="24" customHeight="true">
+      <c r="B16" s="5"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+    </row>
+    <row r="17" ht="24" customHeight="true">
+      <c r="B17" s="5"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+    </row>
+    <row r="18" ht="24" customHeight="true">
+      <c r="B18" s="5"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+    </row>
+    <row r="19" ht="24" customHeight="true">
+      <c r="B19" s="5"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+    </row>
+    <row r="22" ht="22" customHeight="true">
+      <c r="B22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+    </row>
+    <row r="24" ht="33" customHeight="true">
+      <c r="B24" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="true">
+      <c r="B25" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I25" s="5"/>
+    </row>
+    <row r="26" ht="24" customHeight="true">
+      <c r="B26" s="5"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+    </row>
+    <row r="27" ht="24" customHeight="true">
+      <c r="B27" s="5"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+    </row>
+    <row r="28" ht="24" customHeight="true">
+      <c r="B28" s="5"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+    </row>
+    <row r="29" ht="24" customHeight="true">
+      <c r="B29" s="5"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+    </row>
+    <row r="30" ht="24" customHeight="true">
+      <c r="B30" s="5"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="H2:K8"/>
+  <mergeCells count="29">
+    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="B5:I5"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="C7:C10"/>
+    <mergeCell ref="D7:D10"/>
+    <mergeCell ref="E7:E10"/>
+    <mergeCell ref="F7:F10"/>
+    <mergeCell ref="G7:G10"/>
+    <mergeCell ref="H7:H10"/>
+    <mergeCell ref="I7:I10"/>
+    <mergeCell ref="B13:I13"/>
+    <mergeCell ref="B15:B19"/>
+    <mergeCell ref="C15:C19"/>
+    <mergeCell ref="D15:D19"/>
+    <mergeCell ref="E15:E19"/>
+    <mergeCell ref="F15:F19"/>
+    <mergeCell ref="G15:G19"/>
+    <mergeCell ref="H15:H19"/>
+    <mergeCell ref="I15:I19"/>
+    <mergeCell ref="B22:I22"/>
+    <mergeCell ref="B23:I23"/>
+    <mergeCell ref="B25:B30"/>
+    <mergeCell ref="C25:C30"/>
+    <mergeCell ref="D25:D30"/>
+    <mergeCell ref="E25:E30"/>
+    <mergeCell ref="F25:F30"/>
+    <mergeCell ref="G25:G30"/>
+    <mergeCell ref="H25:H30"/>
+    <mergeCell ref="I25:I30"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -616,57 +1448,383 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="7" min="1" width="10"/>
-    <col customWidth="true" max="11" min="8" width="24"/>
+    <col customWidth="true" max="1" min="1" width="3"/>
+    <col customWidth="true" max="2" min="2" width="8"/>
+    <col customWidth="true" max="3" min="3" width="30"/>
+    <col customWidth="true" max="4" min="4" width="28.25"/>
+    <col customWidth="true" max="5" min="5" width="14"/>
+    <col customWidth="true" max="6" min="6" width="30"/>
+    <col customWidth="true" max="8" min="7" width="10"/>
+    <col customWidth="true" max="9" min="9" width="12"/>
   </cols>
   <sheetData>
-    <row r="2" ht="22" customHeight="true">
-      <c r="H2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-    </row>
-    <row r="3" ht="22" customHeight="true">
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-    </row>
-    <row r="4" ht="22" customHeight="true">
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-    </row>
-    <row r="5" ht="22" customHeight="true">
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-    </row>
     <row r="6" ht="22" customHeight="true">
+      <c r="B6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-    </row>
-    <row r="7" ht="22" customHeight="true">
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-    </row>
-    <row r="8" ht="22" customHeight="true">
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+    </row>
+    <row r="8" ht="33" customHeight="true">
+      <c r="B8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="true">
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="5"/>
+    </row>
+    <row r="10" ht="24" customHeight="true">
+      <c r="B10" s="5"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+    </row>
+    <row r="11" ht="24" customHeight="true">
+      <c r="B11" s="5"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+    </row>
+    <row r="12" ht="24" customHeight="true">
+      <c r="B12" s="5"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+    </row>
+    <row r="13" ht="24" customHeight="true">
+      <c r="B13" s="5"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+    </row>
+    <row r="18" ht="22" customHeight="true">
+      <c r="B18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+    </row>
+    <row r="20" ht="33" customHeight="true">
+      <c r="B20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="true">
+      <c r="B21" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I21" s="5"/>
+    </row>
+    <row r="22" ht="24" customHeight="true">
+      <c r="B22" s="5"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+    </row>
+    <row r="23" ht="24" customHeight="true">
+      <c r="B23" s="5"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+    </row>
+    <row r="24" ht="24" customHeight="true">
+      <c r="B24" s="5"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+    </row>
+    <row r="25" ht="24" customHeight="true">
+      <c r="B25" s="5"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+    </row>
+    <row r="26" ht="24" customHeight="true">
+      <c r="B26" s="5"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+    </row>
+    <row r="31" ht="22" customHeight="true">
+      <c r="B31" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+    </row>
+    <row r="32" ht="33" customHeight="true">
+      <c r="B32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="true">
+      <c r="B33" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I33" s="5"/>
+    </row>
+    <row r="34" ht="24" customHeight="true">
+      <c r="B34" s="5"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+    </row>
+    <row r="35" ht="24" customHeight="true">
+      <c r="B35" s="5"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+    </row>
+    <row r="36" ht="24" customHeight="true">
+      <c r="B36" s="5"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+    </row>
+    <row r="37" ht="24" customHeight="true">
+      <c r="B37" s="5"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="H2:K8"/>
+  <mergeCells count="29">
+    <mergeCell ref="B6:I6"/>
+    <mergeCell ref="B7:I7"/>
+    <mergeCell ref="B9:B13"/>
+    <mergeCell ref="C9:C13"/>
+    <mergeCell ref="D9:D13"/>
+    <mergeCell ref="E9:E13"/>
+    <mergeCell ref="F9:F13"/>
+    <mergeCell ref="G9:G13"/>
+    <mergeCell ref="H9:H13"/>
+    <mergeCell ref="I9:I13"/>
+    <mergeCell ref="B18:I18"/>
+    <mergeCell ref="B19:I19"/>
+    <mergeCell ref="B21:B26"/>
+    <mergeCell ref="C21:C26"/>
+    <mergeCell ref="D21:D26"/>
+    <mergeCell ref="E21:E26"/>
+    <mergeCell ref="F21:F26"/>
+    <mergeCell ref="G21:G26"/>
+    <mergeCell ref="H21:H26"/>
+    <mergeCell ref="I21:I26"/>
+    <mergeCell ref="B31:I31"/>
+    <mergeCell ref="B33:B37"/>
+    <mergeCell ref="C33:C37"/>
+    <mergeCell ref="D33:D37"/>
+    <mergeCell ref="E33:E37"/>
+    <mergeCell ref="F33:F37"/>
+    <mergeCell ref="G33:G37"/>
+    <mergeCell ref="H33:H37"/>
+    <mergeCell ref="I33:I37"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/target.xlsx
+++ b/target.xlsx
@@ -689,7 +689,7 @@
     <col customWidth="true" max="1" min="1" width="3"/>
     <col customWidth="true" max="2" min="2" width="8"/>
     <col customWidth="true" max="3" min="3" width="30"/>
-    <col customWidth="true" max="4" min="4" width="28.25"/>
+    <col customWidth="true" max="4" min="4" width="28"/>
     <col customWidth="true" max="5" min="5" width="14"/>
     <col customWidth="true" max="6" min="6" width="30"/>
     <col customWidth="true" max="8" min="7" width="10"/>
@@ -1075,7 +1075,7 @@
     <col customWidth="true" max="1" min="1" width="3"/>
     <col customWidth="true" max="2" min="2" width="8"/>
     <col customWidth="true" max="3" min="3" width="30"/>
-    <col customWidth="true" max="4" min="4" width="28.25"/>
+    <col customWidth="true" max="4" min="4" width="28"/>
     <col customWidth="true" max="5" min="5" width="14"/>
     <col customWidth="true" max="6" min="6" width="30"/>
     <col customWidth="true" max="8" min="7" width="10"/>
@@ -1451,7 +1451,7 @@
     <col customWidth="true" max="1" min="1" width="3"/>
     <col customWidth="true" max="2" min="2" width="8"/>
     <col customWidth="true" max="3" min="3" width="30"/>
-    <col customWidth="true" max="4" min="4" width="28.25"/>
+    <col customWidth="true" max="4" min="4" width="28"/>
     <col customWidth="true" max="5" min="5" width="14"/>
     <col customWidth="true" max="6" min="6" width="30"/>
     <col customWidth="true" max="8" min="7" width="10"/>

--- a/target.xlsx
+++ b/target.xlsx
@@ -76,7 +76,10 @@
   <si>
     <t>OS 설치 진행
 - UEFI 부팅 후 파티션 구성
-- /boot 1GB, swap 4GB</t>
+- /boot 1GB, swap 4GB
+- 3단계: RAID 1 구성 확인
+- 4단계: 커널 파라미터 적용
+- 5단계: NTP 동기화</t>
   </si>
   <si>
     <t>설치 화면 캡처 첨부</t>
@@ -162,7 +165,9 @@
     <t>점검 결과 보고서 작성</t>
   </si>
   <si>
-    <t>점검 결과 화면 확인</t>
+    <t>점검 결과 화면 확인
+- 추가: auditd 규칙 재로딩
+- 추가: 결과 스크린샷 보관</t>
   </si>
 </sst>
 </file>
@@ -270,6 +275,42 @@
 <xdr:wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1228725</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>314325</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 2" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="false"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1371600" cy="342900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="true" fPrintsWithSheet="true"/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>57150</xdr:colOff>
       <xdr:row>16</xdr:row>
@@ -283,7 +324,79 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 2" descr=""/>
+        <xdr:cNvPr id="3" name="Picture 3" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="false"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1371600" cy="342900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="true" fPrintsWithSheet="true"/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1428750</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 4" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="false"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1371600" cy="342900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="true" fPrintsWithSheet="true"/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1428750</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 5" descr=""/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="false"/>
         </xdr:cNvPicPr>
@@ -352,6 +465,42 @@
 <xdr:wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>800100</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 2" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="false"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1371600" cy="342900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="true" fPrintsWithSheet="true"/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>57150</xdr:colOff>
       <xdr:row>23</xdr:row>
@@ -365,7 +514,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 2" descr=""/>
+        <xdr:cNvPr id="3" name="Picture 3" descr=""/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="false"/>
         </xdr:cNvPicPr>
@@ -401,7 +550,43 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 3" descr=""/>
+        <xdr:cNvPr id="4" name="Picture 4" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="false"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1371600" cy="342900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="true" fPrintsWithSheet="true"/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>276225</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1428750</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>247650</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 5" descr=""/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="false"/>
         </xdr:cNvPicPr>
